--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -884,7 +884,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="28275007"/&gt;
   &lt;display value="Total body plethysmography (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -1234,6 +1234,86 @@
 </t>
   </si>
   <si>
+    <t>DiagnosticReport.result:IRV_ERV</t>
+  </si>
+  <si>
+    <t>IRV_ERV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-irv-erv)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:VC</t>
+  </si>
+  <si>
+    <t>VC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-vc)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:FRC</t>
+  </si>
+  <si>
+    <t>FRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-frc)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:R_tot</t>
+  </si>
+  <si>
+    <t>R_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:sR_tot</t>
+  </si>
+  <si>
+    <t>sR_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r-spezifisch)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:sR_eff</t>
+  </si>
+  <si>
+    <t>sR_eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r-effektiv)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:sG_tot</t>
+  </si>
+  <si>
+    <t>sG_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-sg-total)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:TLC</t>
+  </si>
+  <si>
+    <t>TLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-tlc)
+</t>
+  </si>
+  <si>
     <t>DiagnosticReport.result:RV</t>
   </si>
   <si>
@@ -1244,90 +1324,10 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.result:VC</t>
-  </si>
-  <si>
-    <t>VC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-vc)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:FRC</t>
-  </si>
-  <si>
-    <t>FRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-frc)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:R_tot</t>
-  </si>
-  <si>
-    <t>R_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:sR_tot</t>
-  </si>
-  <si>
-    <t>sR_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r-spezifisch)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:sR_eff</t>
-  </si>
-  <si>
-    <t>sR_eff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-r-effektiv)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:sG_tot</t>
-  </si>
-  <si>
-    <t>sG_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-sg-total)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:TLC</t>
-  </si>
-  <si>
-    <t>TLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-tlc)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:RVL</t>
-  </si>
-  <si>
-    <t>RVL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-rvl)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:RVL_TLC</t>
-  </si>
-  <si>
-    <t>RVL_TLC</t>
+    <t>DiagnosticReport.result:RV_TLC</t>
+  </si>
+  <si>
+    <t>RV_TLC</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-rvl-tlc)

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -815,6 +815,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="720449003"/&gt;
   &lt;display value="Pulmonary function report (record artifact)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -884,7 +885,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="28275007"/&gt;
   &lt;display value="Total body plethysmography (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -1482,7 +1483,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
